--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_4.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="90">
   <si>
     <t>Sezione</t>
   </si>
@@ -35,16 +35,22 @@
     <t>Condizioni obbligatorieta'</t>
   </si>
   <si>
+    <t>Allegati</t>
+  </si>
+  <si>
+    <t>Allegato generico</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
     <t>Formula</t>
   </si>
   <si>
     <t>122-bis</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>122-bis.2</t>
@@ -334,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.46484375" customWidth="true" bestFit="true"/>
@@ -394,108 +400,108 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="G5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>22</v>
@@ -504,21 +510,21 @@
         <v>10</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>24</v>
@@ -527,67 +533,67 @@
         <v>10</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>33</v>
@@ -596,21 +602,21 @@
         <v>10</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>35</v>
@@ -619,21 +625,21 @@
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>37</v>
@@ -642,21 +648,21 @@
         <v>10</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>39</v>
@@ -665,127 +671,127 @@
         <v>10</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G19" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>49</v>
@@ -794,99 +800,99 @@
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>33</v>
@@ -895,21 +901,21 @@
         <v>10</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>35</v>
@@ -918,21 +924,21 @@
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>37</v>
@@ -941,21 +947,21 @@
         <v>10</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>39</v>
@@ -964,127 +970,127 @@
         <v>10</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>49</v>
@@ -1093,99 +1099,99 @@
         <v>9</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>50</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F35" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="F36" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>33</v>
@@ -1194,21 +1200,21 @@
         <v>10</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>35</v>
@@ -1217,21 +1223,21 @@
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>37</v>
@@ -1240,21 +1246,21 @@
         <v>10</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>39</v>
@@ -1263,127 +1269,127 @@
         <v>10</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>49</v>
@@ -1392,7 +1398,7 @@
         <v>9</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>50</v>
@@ -1401,21 +1407,21 @@
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>52</v>
@@ -1424,7 +1430,7 @@
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -1432,36 +1438,36 @@
         <v>56</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>58</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>61</v>
@@ -1470,21 +1476,21 @@
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>62</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>63</v>
@@ -1493,21 +1499,21 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>64</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>65</v>
@@ -1516,12 +1522,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>66</v>
@@ -1530,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>67</v>
@@ -1539,12 +1545,12 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>68</v>
@@ -1553,7 +1559,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>69</v>
@@ -1562,12 +1568,12 @@
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>70</v>
@@ -1576,7 +1582,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>71</v>
@@ -1585,12 +1591,12 @@
         <v>10</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>72</v>
@@ -1599,7 +1605,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>73</v>
@@ -1608,12 +1614,12 @@
         <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>74</v>
@@ -1622,7 +1628,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>75</v>
@@ -1631,21 +1637,21 @@
         <v>10</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>76</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>77</v>
@@ -1654,21 +1660,21 @@
         <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>79</v>
@@ -1677,44 +1683,44 @@
         <v>10</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="C59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>85</v>
@@ -1723,30 +1729,53 @@
         <v>10</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>18</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_4.xlsx
+++ b/docs/Mapping_casi_uso/nascita/Dic_Nasc_998_4.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="165">
   <si>
     <t>Sezione</t>
   </si>
@@ -185,7 +185,7 @@
     <t>tipologia</t>
   </si>
   <si>
-    <t>evento.datiAdozioneMinoriInternazionale.tipologia,in,(1,2)</t>
+    <t>evento.datiAdozioneMinoriInternazionale.tipologia,in,(1,2,4)</t>
   </si>
   <si>
     <t>Atto di nascita del soggetto</t>
@@ -565,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.46484375" customWidth="true" bestFit="true"/>
@@ -574,7 +574,7 @@
     <col min="4" max="4" width="54.15234375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="27.3203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="53.73046875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="55.39453125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,7 +651,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
@@ -674,7 +674,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
@@ -697,68 +697,68 @@
         <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -766,7 +766,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>19</v>
@@ -775,7 +775,7 @@
         <v>20</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>10</v>
@@ -789,7 +789,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>19</v>
@@ -798,7 +798,7 @@
         <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>10</v>
@@ -812,7 +812,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>19</v>
@@ -821,7 +821,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>10</v>
@@ -832,25 +832,25 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -858,16 +858,16 @@
         <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>10</v>
@@ -881,7 +881,7 @@
         <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>19</v>
@@ -890,7 +890,7 @@
         <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
@@ -904,7 +904,7 @@
         <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>19</v>
@@ -913,7 +913,7 @@
         <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>10</v>
@@ -927,7 +927,7 @@
         <v>29</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>19</v>
@@ -936,7 +936,7 @@
         <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
@@ -950,16 +950,16 @@
         <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>10</v>
@@ -973,16 +973,16 @@
         <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>10</v>
@@ -996,7 +996,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>19</v>
@@ -1005,7 +1005,7 @@
         <v>31</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>10</v>
@@ -1019,7 +1019,7 @@
         <v>29</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>19</v>
@@ -1028,7 +1028,7 @@
         <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
@@ -1042,19 +1042,19 @@
         <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>33</v>
@@ -1065,7 +1065,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
@@ -1074,7 +1074,7 @@
         <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>50</v>
@@ -1088,7 +1088,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
@@ -1097,7 +1097,7 @@
         <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>50</v>
@@ -1111,19 +1111,19 @@
         <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>33</v>
@@ -1134,22 +1134,22 @@
         <v>29</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -1157,16 +1157,16 @@
         <v>29</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>10</v>
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>19</v>
@@ -1189,7 +1189,7 @@
         <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>10</v>
@@ -1203,7 +1203,7 @@
         <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>19</v>
@@ -1212,7 +1212,7 @@
         <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1226,7 +1226,7 @@
         <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>19</v>
@@ -1235,7 +1235,7 @@
         <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>10</v>
@@ -1249,16 +1249,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>10</v>
@@ -1272,16 +1272,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>10</v>
@@ -1295,7 +1295,7 @@
         <v>29</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>19</v>
@@ -1304,7 +1304,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>19</v>
@@ -1327,7 +1327,7 @@
         <v>31</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1341,19 +1341,19 @@
         <v>29</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>57</v>
@@ -1364,7 +1364,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>9</v>
@@ -1373,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>50</v>
@@ -1387,7 +1387,7 @@
         <v>29</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>9</v>
@@ -1396,7 +1396,7 @@
         <v>31</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>50</v>
@@ -1410,19 +1410,19 @@
         <v>29</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>57</v>
@@ -1430,25 +1430,25 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39">
@@ -1456,16 +1456,16 @@
         <v>58</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>10</v>
@@ -1479,7 +1479,7 @@
         <v>58</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>19</v>
@@ -1488,7 +1488,7 @@
         <v>59</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>10</v>
@@ -1502,7 +1502,7 @@
         <v>58</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>19</v>
@@ -1511,7 +1511,7 @@
         <v>59</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
@@ -1525,7 +1525,7 @@
         <v>58</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>19</v>
@@ -1534,7 +1534,7 @@
         <v>59</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1548,16 +1548,16 @@
         <v>58</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1571,16 +1571,16 @@
         <v>58</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1594,7 +1594,7 @@
         <v>58</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>19</v>
@@ -1603,7 +1603,7 @@
         <v>59</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1617,7 +1617,7 @@
         <v>58</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>19</v>
@@ -1626,7 +1626,7 @@
         <v>59</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1640,16 +1640,16 @@
         <v>58</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1663,7 +1663,7 @@
         <v>58</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>9</v>
@@ -1672,7 +1672,7 @@
         <v>59</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1686,7 +1686,7 @@
         <v>58</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>9</v>
@@ -1695,7 +1695,7 @@
         <v>59</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1709,16 +1709,16 @@
         <v>58</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1729,25 +1729,25 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -1755,7 +1755,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>19</v>
@@ -1764,7 +1764,7 @@
         <v>62</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1778,7 +1778,7 @@
         <v>60</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>19</v>
@@ -1787,7 +1787,7 @@
         <v>62</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1801,16 +1801,16 @@
         <v>60</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1824,7 +1824,7 @@
         <v>60</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>9</v>
@@ -1833,10 +1833,10 @@
         <v>62</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>57</v>
@@ -1847,7 +1847,7 @@
         <v>60</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
@@ -1856,10 +1856,10 @@
         <v>62</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>57</v>
@@ -1870,7 +1870,7 @@
         <v>60</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
@@ -1879,10 +1879,10 @@
         <v>62</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>57</v>
@@ -1893,7 +1893,7 @@
         <v>60</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>9</v>
@@ -1902,10 +1902,10 @@
         <v>62</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>57</v>
@@ -1916,7 +1916,7 @@
         <v>60</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>9</v>
@@ -1925,10 +1925,10 @@
         <v>62</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>57</v>
@@ -1939,19 +1939,19 @@
         <v>60</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>62</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>57</v>
@@ -1962,7 +1962,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>19</v>
@@ -1971,7 +1971,7 @@
         <v>62</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1982,19 +1982,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2008,7 +2008,7 @@
         <v>84</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>19</v>
@@ -2017,7 +2017,7 @@
         <v>86</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2028,22 +2028,22 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>57</v>
@@ -2054,19 +2054,19 @@
         <v>90</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>57</v>
@@ -2077,16 +2077,16 @@
         <v>90</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2100,16 +2100,16 @@
         <v>90</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2123,16 +2123,16 @@
         <v>90</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2146,7 +2146,7 @@
         <v>90</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>9</v>
@@ -2155,10 +2155,10 @@
         <v>92</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>57</v>
@@ -2169,19 +2169,19 @@
         <v>90</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>57</v>
@@ -2192,7 +2192,7 @@
         <v>90</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>19</v>
@@ -2201,7 +2201,7 @@
         <v>92</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>90</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>19</v>
@@ -2224,7 +2224,7 @@
         <v>92</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2238,16 +2238,16 @@
         <v>90</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2261,7 +2261,7 @@
         <v>90</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>9</v>
@@ -2270,10 +2270,10 @@
         <v>92</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>57</v>
@@ -2284,7 +2284,7 @@
         <v>90</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>9</v>
@@ -2293,10 +2293,10 @@
         <v>92</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>57</v>
@@ -2307,7 +2307,7 @@
         <v>90</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>9</v>
@@ -2316,10 +2316,10 @@
         <v>92</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>57</v>
@@ -2330,7 +2330,7 @@
         <v>90</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>9</v>
@@ -2339,7 +2339,7 @@
         <v>92</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>50</v>
@@ -2353,19 +2353,19 @@
         <v>90</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>57</v>
@@ -2376,7 +2376,7 @@
         <v>90</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>19</v>
@@ -2385,7 +2385,7 @@
         <v>92</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2399,19 +2399,19 @@
         <v>90</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>57</v>
@@ -2422,7 +2422,7 @@
         <v>90</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
@@ -2431,7 +2431,7 @@
         <v>92</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>50</v>
@@ -2445,7 +2445,7 @@
         <v>90</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>9</v>
@@ -2454,10 +2454,10 @@
         <v>92</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>57</v>
@@ -2468,7 +2468,7 @@
         <v>90</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>9</v>
@@ -2477,10 +2477,10 @@
         <v>92</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>57</v>
@@ -2491,7 +2491,7 @@
         <v>90</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>9</v>
@@ -2500,10 +2500,10 @@
         <v>92</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>57</v>
@@ -2514,7 +2514,7 @@
         <v>90</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>9</v>
@@ -2523,10 +2523,10 @@
         <v>92</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>57</v>
@@ -2537,7 +2537,7 @@
         <v>90</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>9</v>
@@ -2546,10 +2546,10 @@
         <v>92</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>57</v>
@@ -2560,7 +2560,7 @@
         <v>90</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>9</v>
@@ -2569,10 +2569,10 @@
         <v>92</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>57</v>
@@ -2583,7 +2583,7 @@
         <v>90</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
@@ -2592,7 +2592,7 @@
         <v>92</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>50</v>
@@ -2606,19 +2606,19 @@
         <v>90</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>57</v>
@@ -2629,7 +2629,7 @@
         <v>90</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>19</v>
@@ -2638,7 +2638,7 @@
         <v>92</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2652,7 +2652,7 @@
         <v>90</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>19</v>
@@ -2661,7 +2661,7 @@
         <v>92</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2675,16 +2675,16 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>92</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2698,7 +2698,7 @@
         <v>90</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>9</v>
@@ -2707,10 +2707,10 @@
         <v>92</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>57</v>
@@ -2721,7 +2721,7 @@
         <v>90</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>9</v>
@@ -2730,10 +2730,10 @@
         <v>92</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>57</v>
@@ -2744,7 +2744,7 @@
         <v>90</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>9</v>
@@ -2753,10 +2753,10 @@
         <v>92</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>57</v>
@@ -2767,7 +2767,7 @@
         <v>90</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>9</v>
@@ -2776,7 +2776,7 @@
         <v>92</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>50</v>
@@ -2787,22 +2787,22 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>159</v>
+        <v>90</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>93</v>
+        <v>158</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>57</v>
@@ -2813,19 +2813,19 @@
         <v>159</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>57</v>
@@ -2836,16 +2836,16 @@
         <v>159</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2859,16 +2859,16 @@
         <v>159</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2882,16 +2882,16 @@
         <v>159</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2905,7 +2905,7 @@
         <v>159</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>9</v>
@@ -2914,10 +2914,10 @@
         <v>160</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>57</v>
@@ -2928,19 +2928,19 @@
         <v>159</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>57</v>
@@ -2951,7 +2951,7 @@
         <v>159</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>19</v>
@@ -2960,7 +2960,7 @@
         <v>160</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -2974,7 +2974,7 @@
         <v>159</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>19</v>
@@ -2983,7 +2983,7 @@
         <v>160</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -2997,16 +2997,16 @@
         <v>159</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>159</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>9</v>
@@ -3029,10 +3029,10 @@
         <v>160</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>57</v>
@@ -3043,7 +3043,7 @@
         <v>159</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>9</v>
@@ -3052,10 +3052,10 @@
         <v>160</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>57</v>
@@ -3066,7 +3066,7 @@
         <v>159</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>9</v>
@@ -3075,10 +3075,10 @@
         <v>160</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
         <v>57</v>
@@ -3089,7 +3089,7 @@
         <v>159</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>9</v>
@@ -3098,7 +3098,7 @@
         <v>160</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>50</v>
@@ -3112,19 +3112,19 @@
         <v>159</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>57</v>
@@ -3135,7 +3135,7 @@
         <v>159</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>19</v>
@@ -3144,7 +3144,7 @@
         <v>160</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
@@ -3158,19 +3158,19 @@
         <v>159</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
         <v>57</v>
@@ -3181,7 +3181,7 @@
         <v>159</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>9</v>
@@ -3190,7 +3190,7 @@
         <v>160</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>50</v>
@@ -3204,7 +3204,7 @@
         <v>159</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>9</v>
@@ -3213,10 +3213,10 @@
         <v>160</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>57</v>
@@ -3227,7 +3227,7 @@
         <v>159</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>9</v>
@@ -3236,10 +3236,10 @@
         <v>160</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>57</v>
@@ -3250,7 +3250,7 @@
         <v>159</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>9</v>
@@ -3259,10 +3259,10 @@
         <v>160</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>57</v>
@@ -3273,7 +3273,7 @@
         <v>159</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>9</v>
@@ -3282,10 +3282,10 @@
         <v>160</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>57</v>
@@ -3296,7 +3296,7 @@
         <v>159</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>9</v>
@@ -3305,10 +3305,10 @@
         <v>160</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>57</v>
@@ -3319,7 +3319,7 @@
         <v>159</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>9</v>
@@ -3328,10 +3328,10 @@
         <v>160</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>57</v>
@@ -3342,7 +3342,7 @@
         <v>159</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>9</v>
@@ -3351,7 +3351,7 @@
         <v>160</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>50</v>
@@ -3365,19 +3365,19 @@
         <v>159</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>57</v>
@@ -3388,7 +3388,7 @@
         <v>159</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>19</v>
@@ -3397,7 +3397,7 @@
         <v>160</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>159</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>19</v>
@@ -3420,7 +3420,7 @@
         <v>160</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>10</v>
@@ -3434,16 +3434,16 @@
         <v>159</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>160</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>10</v>
@@ -3457,7 +3457,7 @@
         <v>159</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>9</v>
@@ -3466,10 +3466,10 @@
         <v>160</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>57</v>
@@ -3480,7 +3480,7 @@
         <v>159</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>9</v>
@@ -3489,10 +3489,10 @@
         <v>160</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>57</v>
@@ -3503,7 +3503,7 @@
         <v>159</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>9</v>
@@ -3512,10 +3512,10 @@
         <v>160</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>57</v>
@@ -3526,7 +3526,7 @@
         <v>159</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>9</v>
@@ -3535,7 +3535,7 @@
         <v>160</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>50</v>
@@ -3546,25 +3546,25 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>86</v>
+        <v>160</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
     </row>
     <row r="131">
@@ -3572,7 +3572,7 @@
         <v>161</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>19</v>
@@ -3581,12 +3581,35 @@
         <v>86</v>
       </c>
       <c r="E131" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F131" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G131" s="2" t="s">
+      <c r="F132" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G132" s="2" t="s">
         <v>22</v>
       </c>
     </row>
